--- a/data/trans_dic/P04D$colectiva-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,03</t>
+          <t>0,55; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,41</t>
+          <t>0,12; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,33</t>
+          <t>2,24; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,68</t>
+          <t>1,12; 2,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,29</t>
+          <t>0,64; 2,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,75</t>
+          <t>2,01; 3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,11</t>
+          <t>1,03; 2,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,59</t>
+          <t>0,53; 1,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,03</t>
+          <t>2,32; 3,95</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,36</t>
+          <t>2,7; 4,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,11</t>
+          <t>1,76; 3,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,9</t>
+          <t>3,22; 5,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,59</t>
+          <t>1,97; 3,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,55</t>
+          <t>1,35; 2,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,68</t>
+          <t>3,4; 5,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,63</t>
+          <t>2,52; 3,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,58</t>
+          <t>1,7; 2,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,44</t>
+          <t>3,61; 5,35</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,48</t>
+          <t>4,4; 8,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,44</t>
+          <t>5,41; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,11</t>
+          <t>10,25; 15,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,82</t>
+          <t>3,74; 8,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,44</t>
+          <t>4,82; 9,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 16,15</t>
+          <t>11,72; 16,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,64</t>
+          <t>4,44; 7,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,01</t>
+          <t>5,81; 8,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 14,98</t>
+          <t>11,34; 14,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,8</t>
+          <t>2,61; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,4</t>
+          <t>2,26; 3,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,92</t>
+          <t>4,5; 6,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,3</t>
+          <t>2,18; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,06</t>
+          <t>2,02; 3,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 6,72</t>
+          <t>4,82; 6,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,35</t>
+          <t>2,54; 3,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,06</t>
+          <t>2,26; 3,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 6,6</t>
+          <t>5,14; 6,63</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción colectiva en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción colectiva en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6028; 19757</t>
+          <t>5392; 19613</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>907; 10610</t>
+          <t>907; 8977</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11182; 27318</t>
+          <t>11478; 27551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15133; 35851</t>
+          <t>15004; 35879</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6233; 22790</t>
+          <t>6389; 22557</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15305; 28303</t>
+          <t>15194; 28045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23828; 48686</t>
+          <t>23908; 49969</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9058; 27885</t>
+          <t>9251; 26736</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30235; 51070</t>
+          <t>29364; 50056</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52088; 85400</t>
+          <t>52947; 85339</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35473; 64563</t>
+          <t>36533; 64865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72546; 134986</t>
+          <t>73610; 134664</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34204; 62914</t>
+          <t>34596; 62566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26713; 50625</t>
+          <t>26910; 51508</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72773; 126804</t>
+          <t>75842; 124436</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92502; 134937</t>
+          <t>93732; 136493</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66579; 104873</t>
+          <t>69260; 106739</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>164291; 246047</t>
+          <t>163204; 241866</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19973; 40804</t>
+          <t>21149; 43119</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30749; 57089</t>
+          <t>29585; 55830</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64549; 97692</t>
+          <t>66272; 98456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16649; 35880</t>
+          <t>17176; 37214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27896; 51853</t>
+          <t>26467; 51338</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75551; 106326</t>
+          <t>77148; 105897</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43345; 71831</t>
+          <t>41745; 71517</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62491; 98778</t>
+          <t>63649; 98579</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>151797; 195484</t>
+          <t>147937; 194838</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88019; 129517</t>
+          <t>89084; 131649</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75541; 114887</t>
+          <t>76448; 114668</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157134; 238284</t>
+          <t>154995; 236071</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77861; 117170</t>
+          <t>77250; 117264</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70247; 107926</t>
+          <t>71278; 109602</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>171224; 244930</t>
+          <t>175683; 246621</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175764; 233441</t>
+          <t>176731; 233635</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>155648; 211342</t>
+          <t>155907; 209310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>361683; 468050</t>
+          <t>364576; 470304</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$colectiva-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P04D$colectiva-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,02</t>
+          <t>0,58; 1,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,19</t>
+          <t>0,17; 1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,37</t>
+          <t>1,91; 4,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,68</t>
+          <t>1,15; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,27</t>
+          <t>0,66; 2,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,72</t>
+          <t>1,97; 3,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,16</t>
+          <t>1,02; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,53</t>
+          <t>0,55; 1,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,95</t>
+          <t>2,32; 3,85</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,36</t>
+          <t>2,71; 4,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,12</t>
+          <t>1,72; 3,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,89</t>
+          <t>3,73; 5,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,57</t>
+          <t>1,96; 3,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,59</t>
+          <t>1,36; 2,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,57</t>
+          <t>4,18; 5,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,68</t>
+          <t>2,56; 3,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,63</t>
+          <t>1,66; 2,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,35</t>
+          <t>4,27; 5,6</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,96</t>
+          <t>4,13; 8,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 10,21</t>
+          <t>5,58; 10,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,23</t>
+          <t>9,53; 14,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,11</t>
+          <t>3,76; 8,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,35</t>
+          <t>5,02; 9,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,09</t>
+          <t>11,29; 15,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,61</t>
+          <t>4,3; 7,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,99</t>
+          <t>5,89; 9,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 14,93</t>
+          <t>10,88; 14,32</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,86</t>
+          <t>2,64; 3,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,39</t>
+          <t>2,3; 3,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,85</t>
+          <t>5,09; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,3</t>
+          <t>2,24; 3,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,1</t>
+          <t>1,99; 3,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,76</t>
+          <t>5,49; 6,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,36</t>
+          <t>2,59; 3,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,03</t>
+          <t>2,27; 3,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,63</t>
+          <t>5,43; 6,51</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>17886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38974</t>
+          <t>40713</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5392; 19613</t>
+          <t>5639; 18621</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>907; 8977</t>
+          <t>1245; 9175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11478; 27551</t>
+          <t>11011; 26490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15004; 35879</t>
+          <t>15449; 36493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6389; 22557</t>
+          <t>6591; 21401</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15194; 28045</t>
+          <t>16219; 31461</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23908; 49969</t>
+          <t>23465; 48474</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9251; 26736</t>
+          <t>9654; 27756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29364; 50056</t>
+          <t>32398; 53779</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104476</t>
+          <t>105889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>103365</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>213313</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52947; 85339</t>
+          <t>52990; 85619</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36533; 64865</t>
+          <t>35613; 63364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73610; 134664</t>
+          <t>82829; 127749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34596; 62566</t>
+          <t>34452; 62308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26910; 51508</t>
+          <t>27055; 52638</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75842; 124436</t>
+          <t>90472; 126082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93732; 136493</t>
+          <t>95127; 138705</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69260; 106739</t>
+          <t>67516; 104031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163204; 241866</t>
+          <t>187529; 245782</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80568</t>
+          <t>82637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90485</t>
+          <t>98037</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171053</t>
+          <t>180675</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21149; 43119</t>
+          <t>19888; 41741</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29585; 55830</t>
+          <t>30537; 56180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66272; 98456</t>
+          <t>67814; 100930</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17176; 37214</t>
+          <t>17251; 37536</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26467; 51338</t>
+          <t>27576; 52139</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77148; 105897</t>
+          <t>82592; 116855</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41745; 71517</t>
+          <t>40434; 70485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63649; 98579</t>
+          <t>64549; 98972</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147937; 194838</t>
+          <t>157087; 206637</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202921</t>
+          <t>206412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>417867</t>
+          <t>434701</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89084; 131649</t>
+          <t>90213; 130688</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76448; 114668</t>
+          <t>77670; 116521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154995; 236071</t>
+          <t>178826; 235916</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77250; 117264</t>
+          <t>79674; 117639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71278; 109602</t>
+          <t>70340; 110313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>175683; 246621</t>
+          <t>204327; 256819</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>176731; 233635</t>
+          <t>180205; 236211</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>155907; 209310</t>
+          <t>156691; 210080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>364576; 470304</t>
+          <t>392575; 470327</t>
         </is>
       </c>
     </row>
